--- a/code-book.xlsx
+++ b/code-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mynyenrode-my.sharepoint.com/personal/d_luttik_my_nyenrode_nl/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="8_{7AA3FB50-281E-4B67-8AC2-E032B9CDF9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF8FF28-0EB5-4E3E-8E2C-1A1B0495C10C}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="8_{7AA3FB50-281E-4B67-8AC2-E032B9CDF9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A189DEB8-B3AA-4280-BE09-7177B286EABE}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{7C985A53-FB25-4C6B-BDB6-0E24003E9E6B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="154">
   <si>
     <t>Experimenting</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Having the right tooling</t>
   </si>
   <si>
-    <t>Having a strong MarTech stack present &amp; Having data available and accessible (typically requires data-infrastructure)</t>
-  </si>
-  <si>
     <t>Championing AI</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>ROAS optimization</t>
   </si>
   <si>
-    <t>ROAS optimization &amp;</t>
-  </si>
-  <si>
     <t>Agentic Sales agent (inbound or outbound)</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t xml:space="preserve">And the next CMO needs to be CTO’s best friend. And then I’m always like, “Yes, I am,” because it’s actually like, without the technology, I wouldn’t be able to. </t>
   </si>
   <si>
-    <t>Focussing (AI strategy on...) &amp; Lacking focus or structure</t>
-  </si>
-  <si>
     <t>Experiencing resisting</t>
   </si>
   <si>
@@ -416,9 +407,6 @@
     <t>Determining input</t>
   </si>
   <si>
-    <t>Interpreting becomes more important (requires expertise) &amp; Evaluating output</t>
-  </si>
-  <si>
     <t>Evaluating output</t>
   </si>
   <si>
@@ -434,9 +422,6 @@
     <t>Experiencing pressure to adopt</t>
   </si>
   <si>
-    <t>Experiencing pressure</t>
-  </si>
-  <si>
     <t>Seeing transformation potential</t>
   </si>
   <si>
@@ -449,9 +434,6 @@
     <t>Imagining future use cases</t>
   </si>
   <si>
-    <t>Benefit: The AI itself keeps improving (getting better) &amp; Improvements over time</t>
-  </si>
-  <si>
     <t>Towards future:: AI is the future of our company</t>
   </si>
   <si>
@@ -464,9 +446,6 @@
     <t>Just do it / intrinsic motivation</t>
   </si>
   <si>
-    <t>Future usecase: Simulations of respones &amp; Future usecase: Want to create email flows with Agnetic AI</t>
-  </si>
-  <si>
     <t>Creating agents that assist customer</t>
   </si>
   <si>
@@ -507,6 +486,21 @@
   </si>
   <si>
     <t>clarity (in general)</t>
+  </si>
+  <si>
+    <t>Having data &amp; tools available and accessible (typically requires data-infrastructure)</t>
+  </si>
+  <si>
+    <t>Foccussing</t>
+  </si>
+  <si>
+    <t>General purpose personal assistant</t>
+  </si>
+  <si>
+    <t>Benefit: The AI itself keeps improving (getting better)</t>
+  </si>
+  <si>
+    <t>Future usecases</t>
   </si>
 </sst>
 </file>
@@ -613,20 +607,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -978,52 +969,51 @@
     <col min="2" max="2" width="20.89453125" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.15625" style="2" customWidth="1"/>
     <col min="4" max="4" width="27.20703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38.9453125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="8.83984375" style="13"/>
+    <col min="5" max="5" width="38.9453125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="8.83984375" style="10"/>
     <col min="7" max="16384" width="8.83984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="9" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" s="7" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1031,16 +1021,16 @@
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -1050,7 +1040,7 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1058,23 +1048,23 @@
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>155</v>
+      <c r="E8" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1082,53 +1072,51 @@
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:7" s="7" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="E11" s="14" t="s">
+      <c r="C11" s="8"/>
+      <c r="E11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="14"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>33</v>
+      <c r="B12" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="E13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="12"/>
+      <c r="E13" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1136,17 +1124,17 @@
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="15"/>
+      <c r="E15" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="12"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1155,483 +1143,481 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="9" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="E22" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="14"/>
+    <row r="22" spans="1:6" s="7" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="E22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>39</v>
+        <v>117</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>38</v>
+        <v>108</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="E26" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" s="9" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="E28" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="14"/>
+    </row>
+    <row r="28" spans="1:6" s="7" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="E28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>53</v>
+        <v>113</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>56</v>
+        <v>46</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="13" t="s">
         <v>62</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>66</v>
+        <v>58</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A38" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>72</v>
+        <v>135</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A39" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>102</v>
+        <v>73</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A40" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>103</v>
+        <v>120</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A41" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>125</v>
+        <v>72</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="7" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="E44" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" s="9" customFormat="1" ht="13.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="E44" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F44" s="14"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A45" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>69</v>
+        <v>139</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A47" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>93</v>
+        <v>140</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A48" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>92</v>
+        <v>141</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A49" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>91</v>
+        <v>142</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A50" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>94</v>
+        <v>143</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A51" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>90</v>
+        <v>144</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A52" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>95</v>
+        <v>69</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A54" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>89</v>
+        <v>145</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A55" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A56" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>96</v>
+        <v>78</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A58" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>97</v>
+        <v>79</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A59" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>98</v>
+        <v>80</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A60" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A61" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E61" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F62" s="16"/>
+      <c r="E61" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A62" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" s="13"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A63" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>137</v>
+        <v>125</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C64" s="1"/>
-      <c r="E64" s="13" t="s">
-        <v>144</v>
+      <c r="E64" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A65" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C65" s="1"/>
-      <c r="E65" s="13" t="s">
-        <v>138</v>
+      <c r="E65" s="10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A66" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C66" s="1"/>
-      <c r="E66" s="13" t="s">
-        <v>141</v>
+      <c r="E66" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A67" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C67" s="1"/>
-      <c r="E67" s="13" t="s">
-        <v>139</v>
+      <c r="E67" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A68" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68" s="13" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/code-book.xlsx
+++ b/code-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F7C995-638A-4BAE-B257-6BF0EA3C24C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C518346-9A5F-4968-85D0-BE45C7AD3470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="152">
   <si>
     <t>Descriptive coding</t>
   </si>
@@ -368,12 +368,6 @@
   </si>
   <si>
     <t>Feeling in control</t>
-  </si>
-  <si>
-    <t>Experiencing more fun</t>
-  </si>
-  <si>
-    <t>more fun</t>
   </si>
   <si>
     <t>Gaining improved personalization</t>
@@ -488,7 +482,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,6 +543,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -588,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -601,10 +617,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="29.5234375" style="1" customWidth="1"/>
@@ -947,7 +968,7 @@
     <col min="3" max="3" width="17.15625" style="2" customWidth="1"/>
     <col min="4" max="4" width="27.20703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.9453125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="8.83984375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="8.83984375" style="18" customWidth="1"/>
     <col min="7" max="7" width="8.83984375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.83984375" style="1"/>
   </cols>
@@ -968,7 +989,7 @@
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5"/>
@@ -986,7 +1007,7 @@
       <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="14">
         <v>37</v>
       </c>
     </row>
@@ -997,7 +1018,7 @@
       <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="14">
         <v>28</v>
       </c>
     </row>
@@ -1008,7 +1029,7 @@
       <c r="E4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="14">
         <v>24</v>
       </c>
     </row>
@@ -1019,7 +1040,7 @@
       <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="14">
         <v>8</v>
       </c>
     </row>
@@ -1033,7 +1054,7 @@
       <c r="E6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="14">
         <v>24</v>
       </c>
     </row>
@@ -1044,7 +1065,7 @@
       <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="14">
         <v>1</v>
       </c>
     </row>
@@ -1055,7 +1076,7 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="14">
         <v>18</v>
       </c>
     </row>
@@ -1066,7 +1087,7 @@
       <c r="E9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1077,7 +1098,7 @@
       <c r="E10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="14">
         <v>14</v>
       </c>
     </row>
@@ -1089,7 +1110,7 @@
       <c r="E11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="15">
         <v>4</v>
       </c>
     </row>
@@ -1107,18 +1128,18 @@
       <c r="E12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="14">
         <v>2</v>
       </c>
     </row>
@@ -1132,7 +1153,7 @@
       <c r="E14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="14">
         <v>21</v>
       </c>
     </row>
@@ -1143,7 +1164,7 @@
       <c r="E15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="16">
         <v>21</v>
       </c>
       <c r="G15" s="2"/>
@@ -1155,7 +1176,7 @@
       <c r="E16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1169,7 +1190,7 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="14">
         <v>16</v>
       </c>
     </row>
@@ -1180,7 +1201,7 @@
       <c r="E18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="14">
         <v>13</v>
       </c>
     </row>
@@ -1194,7 +1215,7 @@
       <c r="E19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="14">
         <v>1</v>
       </c>
     </row>
@@ -1205,7 +1226,7 @@
       <c r="E20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1216,7 +1237,7 @@
       <c r="E21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1228,7 +1249,7 @@
       <c r="E22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="15">
         <v>7</v>
       </c>
     </row>
@@ -1245,7 +1266,7 @@
       <c r="E23" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="14">
         <v>28</v>
       </c>
     </row>
@@ -1256,7 +1277,7 @@
       <c r="E24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1270,7 +1291,7 @@
       <c r="E25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="14">
         <v>21</v>
       </c>
     </row>
@@ -1281,7 +1302,7 @@
       <c r="E26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="14">
         <v>3</v>
       </c>
     </row>
@@ -1295,7 +1316,7 @@
       <c r="E27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1307,7 +1328,7 @@
       <c r="E28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1324,7 +1345,7 @@
       <c r="E29" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="14">
         <v>39</v>
       </c>
     </row>
@@ -1335,7 +1356,7 @@
       <c r="E30" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="14">
         <v>28</v>
       </c>
     </row>
@@ -1346,7 +1367,7 @@
       <c r="E31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="14">
         <v>4</v>
       </c>
     </row>
@@ -1357,7 +1378,7 @@
       <c r="E32" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="14">
         <v>28</v>
       </c>
     </row>
@@ -1368,7 +1389,7 @@
       <c r="E33" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1379,7 +1400,7 @@
       <c r="E34" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="14">
         <v>21</v>
       </c>
     </row>
@@ -1390,7 +1411,7 @@
       <c r="E35" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="14">
         <v>15</v>
       </c>
     </row>
@@ -1401,7 +1422,7 @@
       <c r="E36" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1412,7 +1433,7 @@
       <c r="E37" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1423,7 +1444,7 @@
       <c r="E38" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="14">
         <v>7</v>
       </c>
     </row>
@@ -1437,7 +1458,7 @@
       <c r="E39" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="14">
         <v>11</v>
       </c>
     </row>
@@ -1448,7 +1469,7 @@
       <c r="E40" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="14">
         <v>14</v>
       </c>
     </row>
@@ -1462,7 +1483,7 @@
       <c r="E41" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="14">
         <v>8</v>
       </c>
     </row>
@@ -1473,7 +1494,7 @@
       <c r="E42" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="14">
         <v>4</v>
       </c>
     </row>
@@ -1484,7 +1505,7 @@
       <c r="E43" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="14">
         <v>4</v>
       </c>
     </row>
@@ -1496,7 +1517,7 @@
       <c r="E44" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1513,7 +1534,7 @@
       <c r="E45" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="14">
         <v>42</v>
       </c>
     </row>
@@ -1524,7 +1545,7 @@
       <c r="E46" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="14">
         <v>25</v>
       </c>
     </row>
@@ -1535,7 +1556,7 @@
       <c r="E47" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="14">
         <v>16</v>
       </c>
     </row>
@@ -1546,7 +1567,7 @@
       <c r="E48" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="14">
         <v>14</v>
       </c>
     </row>
@@ -1557,7 +1578,7 @@
       <c r="E49" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="14">
         <v>14</v>
       </c>
     </row>
@@ -1568,7 +1589,7 @@
       <c r="E50" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="14">
         <v>11</v>
       </c>
     </row>
@@ -1579,7 +1600,7 @@
       <c r="E51" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="14">
         <v>21</v>
       </c>
     </row>
@@ -1590,7 +1611,7 @@
       <c r="E52" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="14">
         <v>3</v>
       </c>
     </row>
@@ -1601,33 +1622,33 @@
       <c r="E53" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F53">
-        <v>1</v>
+      <c r="F53" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>118</v>
       </c>
+      <c r="B54" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="E54" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F54">
-        <v>14</v>
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F55">
-        <v>10</v>
+      <c r="F55" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -1637,33 +1658,33 @@
       <c r="E56" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F56">
-        <v>5</v>
+      <c r="F56" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="B57" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="E57" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F57">
-        <v>3</v>
+        <v>127</v>
+      </c>
+      <c r="F57" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F58">
-        <v>11</v>
+      <c r="F58" s="14">
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -1673,8 +1694,8 @@
       <c r="E59" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F59">
-        <v>12</v>
+      <c r="F59" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -1684,59 +1705,63 @@
       <c r="E60" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A61" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="17">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="4" t="s">
+    <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F62" s="13">
-        <v>7</v>
+      <c r="F62" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="C63" s="1"/>
       <c r="E63" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F63">
-        <v>2</v>
+      <c r="F63" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>142</v>
       </c>
+      <c r="B64" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="C64" s="1"/>
       <c r="E64" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F64">
-        <v>5</v>
+      <c r="F64" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -1744,29 +1769,26 @@
         <v>144</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F65">
-        <v>6</v>
+        <v>146</v>
+      </c>
+      <c r="F65" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B66" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C66" s="1"/>
       <c r="E66" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F66">
-        <v>3</v>
+      <c r="F66" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -1777,23 +1799,12 @@
       <c r="E67" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F68">
+      <c r="F67" s="14">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>